--- a/output/full_scan/batch_seq1_2026-07-06.xlsx
+++ b/output/full_scan/batch_seq1_2026-07-06.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O130"/>
+  <dimension ref="A1:O133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -686,21 +686,21 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1465</v>
+        <v>1303</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>815.978265920637</v>
+        <v>832.2040000116217</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13.65</v>
+        <v>185</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>79.47527433910284</v>
+        <v>74.12175246658413</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>20.73837528914236</v>
+        <v>41.76542440102394</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>4.697826592063701</v>
+        <v>0.3737668920252916</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.0806221395568137</v>
+        <v>4.681439168873602</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1563</v>
+        <v>1465</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>810.8874439430406</v>
+        <v>815.978265920637</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>71</v>
+        <v>13.65</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>65.17099381219026</v>
+        <v>79.47527433910284</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>38.77179694629917</v>
+        <v>20.73837528914236</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.004906277951412</v>
+        <v>4.697826592063701</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.09132543989713229</v>
+        <v>0.0806221395568137</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1440</v>
+        <v>1563</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>791.6567289667439</v>
+        <v>810.8874439430406</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>14.6</v>
+        <v>71</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>66.70851740675525</v>
+        <v>65.17099381219026</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>23.89453547318944</v>
+        <v>38.77179694629917</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3.601385955477169</v>
+        <v>2.004906277951412</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.0952574726495157</v>
+        <v>-0.09132543989713229</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1310</v>
+        <v>1440</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>766.1217400190163</v>
+        <v>791.6567289667439</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>74.36221400742284</v>
+        <v>66.70851740675525</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>37.72289067683151</v>
+        <v>23.89453547318944</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3.71217400190163</v>
+        <v>3.601385955477169</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2261209909354731</v>
+        <v>0.0952574726495157</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1312</v>
+        <v>1447</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>764.918069431586</v>
+        <v>782.9940967049067</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>14.15</v>
+        <v>9.51</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>56.347326615012</v>
+        <v>79.03240040232177</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>34.36618957046324</v>
+        <v>40.92597675358358</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.091806943158602</v>
+        <v>2.899409670490672</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.027310459515917</v>
+        <v>0.3675871488167953</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>754</v>
+        <v>766.1217400190163</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>83.6596282419893</v>
+        <v>74.36221400742284</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>31.48478471959482</v>
+        <v>37.72289067683151</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>5.620206019952386</v>
+        <v>3.71217400190163</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2289069321499406</v>
+        <v>0.2261209909354731</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1434</v>
+        <v>1312</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>752.9004725686719</v>
+        <v>764.918069431586</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>18.95</v>
+        <v>14.15</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>74.72096231178065</v>
+        <v>56.347326615012</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>27.07732619356965</v>
+        <v>34.36618957046324</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.890047256867198</v>
+        <v>2.091806943158602</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.18625119947515</v>
+        <v>0.027310459515917</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1536</v>
+        <v>1314</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>751.2402533275201</v>
+        <v>754</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>53.1</v>
+        <v>10.4</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>61.3909728486936</v>
+        <v>83.6596282419893</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>13.93266737304614</v>
+        <v>31.48478471959482</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.849456816085622</v>
+        <v>5.620206019952386</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.5262513496682548</v>
+        <v>0.2289069321499406</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1418</v>
+        <v>1434</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>749</v>
+        <v>752.9004725686719</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>18.55</v>
+        <v>18.95</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>55.14826449754662</v>
+        <v>74.72096231178065</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15.90634784481706</v>
+        <v>27.07732619356965</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>6.178910599279554</v>
+        <v>2.890047256867198</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.0322822874404478</v>
+        <v>0.18625119947515</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1339</v>
+        <v>1536</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>736.283768023982</v>
+        <v>751.2402533275201</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>45.45</v>
+        <v>53.1</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>62.55636817109538</v>
+        <v>61.3909728486936</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>17.87424386126864</v>
+        <v>13.93266737304614</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.374061271646317</v>
+        <v>1.849456816085622</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.0313654541757503</v>
+        <v>0.5262513496682548</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1409</v>
+        <v>1418</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>733.9723888032323</v>
+        <v>749</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>30.25</v>
+        <v>18.55</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>65.45214539366324</v>
+        <v>55.14826449754662</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>26.12789711452634</v>
+        <v>15.90634784481706</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>4.149646924867155</v>
+        <v>6.178910599279554</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.0456916933259603</v>
+        <v>0.0322822874404478</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1323</v>
+        <v>1339</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>697.8682778544616</v>
+        <v>736.283768023982</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>20.5</v>
+        <v>45.45</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>60.62052541313842</v>
+        <v>62.55636817109538</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>17.57859020504312</v>
+        <v>17.87424386126864</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2.124961138706966</v>
+        <v>1.374061271646317</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0835391095292479</v>
+        <v>0.0313654541757503</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>macd_golden_cross, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1515</v>
+        <v>1409</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>696.8822825809468</v>
+        <v>733.9723888032323</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>42.75</v>
+        <v>30.25</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>90.3086750028726</v>
+        <v>65.45214539366324</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>51.10952485050269</v>
+        <v>26.12789711452634</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.788228258094684</v>
+        <v>4.149646924867155</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.66317935205612</v>
+        <v>0.0456916933259603</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1444</v>
+        <v>1323</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>696.7129017485685</v>
+        <v>697.8682778544616</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>9.15</v>
+        <v>20.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>68.78641669949</v>
+        <v>60.62052541313842</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>43.79157792924845</v>
+        <v>17.57859020504312</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.066024053839308</v>
+        <v>2.124961138706966</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.2449082738335618</v>
+        <v>0.0835391095292479</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>678.2129109248862</v>
+        <v>696.8822825809468</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>11.35</v>
+        <v>42.75</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>71.67215708508529</v>
+        <v>90.3086750028726</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>24.27370318526066</v>
+        <v>51.10952485050269</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.921291092488612</v>
+        <v>2.788228258094684</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.08990219037240341</v>
+        <v>1.66317935205612</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1313</v>
+        <v>1444</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>672.5611132056897</v>
+        <v>696.7129017485685</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>13.55</v>
+        <v>9.15</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>64.8518128534248</v>
+        <v>68.78641669949</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>37.11794954997923</v>
+        <v>43.79157792924845</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3.196624726859515</v>
+        <v>2.066024053839308</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.2199416104209758</v>
+        <v>0.2449082738335618</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1464</v>
+        <v>1517</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>665.1648736658406</v>
+        <v>678.2129109248862</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>11.1</v>
+        <v>11.35</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>72.88985636332505</v>
+        <v>71.67215708508529</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>23.28269051901129</v>
+        <v>24.27370318526066</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.616487366584054</v>
+        <v>1.921291092488612</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.0890519407102992</v>
+        <v>0.08990219037240341</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1210</v>
+        <v>1313</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>664.116607631479</v>
+        <v>672.5611132056897</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>58.8</v>
+        <v>13.55</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>77.84994391340109</v>
+        <v>64.8518128534248</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>39.26148049147232</v>
+        <v>37.11794954997923</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8675364021496641</v>
+        <v>3.196624726859515</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.3137833420867014</v>
+        <v>0.2199416104209758</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1217</v>
+        <v>1464</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>657.8127829306057</v>
+        <v>665.1648736658406</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>10.2</v>
+        <v>11.1</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>71.5700376169147</v>
+        <v>72.88985636332505</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>19.35494223546887</v>
+        <v>23.28269051901129</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.715716297390582</v>
+        <v>1.616487366584054</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.0341066884195914</v>
+        <v>0.0890519407102992</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1560</v>
+        <v>1210</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>652.9661288047052</v>
+        <v>664.116607631479</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>745</v>
+        <v>58.8</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>57.48304344591779</v>
+        <v>77.84994391340109</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>23.6393529206416</v>
+        <v>39.26148049147232</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.4223559501566031</v>
+        <v>0.8675364021496641</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>2.080077874649248</v>
+        <v>0.3137833420867014</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1326</v>
+        <v>1217</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>640.6594292359428</v>
+        <v>657.8127829306057</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>71.19056034291086</v>
+        <v>71.5700376169147</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>27.36833972601967</v>
+        <v>19.35494223546887</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.880104983811955</v>
+        <v>1.715716297390582</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.305100715117758</v>
+        <v>0.0341066884195914</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1102</v>
+        <v>1560</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>636.4422868133917</v>
+        <v>652.9661288047052</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>36.55</v>
+        <v>745</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>62.82528653349475</v>
+        <v>57.48304344591779</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>20.79271091888238</v>
+        <v>23.6393529206416</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.560929032416315</v>
+        <v>0.4223559501566031</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.08209420173603491</v>
+        <v>2.080077874649248</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1503</v>
+        <v>1326</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>621.4592462485612</v>
+        <v>640.6594292359428</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>241.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>58.12545556016688</v>
+        <v>71.19056034291086</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>19.78745357564778</v>
+        <v>27.36833972601967</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.7613849905390745</v>
+        <v>2.880104983811955</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-1.043950873704926</v>
+        <v>1.305100715117758</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1558</v>
+        <v>1102</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>612.1425567224783</v>
+        <v>636.4422868133917</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>92.8</v>
+        <v>36.55</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>65.45129198795441</v>
+        <v>62.82528653349475</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>12.14354605116635</v>
+        <v>20.79271091888238</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.644190855095337</v>
+        <v>0.560929032416315</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.1970516472301099</v>
+        <v>0.08209420173603491</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1321</v>
+        <v>1503</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>611.7139287928117</v>
+        <v>621.4592462485612</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>32.1</v>
+        <v>241.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>63.1668551281756</v>
+        <v>58.12545556016688</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>30.91644696713742</v>
+        <v>19.78745357564778</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.6638936853310556</v>
+        <v>0.7613849905390745</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0775763876004512</v>
+        <v>-1.043950873704926</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1201</v>
+        <v>1558</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>609.9327444363614</v>
+        <v>612.1425567224783</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>12.7</v>
+        <v>92.8</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>60.62950880295568</v>
+        <v>65.45129198795441</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>17.93956228078887</v>
+        <v>12.14354605116635</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.890413683160918</v>
+        <v>1.644190855095337</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0321734798898357</v>
+        <v>0.1970516472301099</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2064,21 +2064,21 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1410</v>
+        <v>1321</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>609.1476411682221</v>
+        <v>611.7139287928117</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>26.2</v>
+        <v>32.1</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>55.18966469322424</v>
+        <v>63.1668551281756</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>17.98372371074881</v>
+        <v>30.91644696713742</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>3.127986603271433</v>
+        <v>0.6638936853310556</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.2687552630880511</v>
+        <v>0.0775763876004512</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1513</v>
+        <v>1201</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>607.1997643304441</v>
+        <v>609.9327444363614</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>178.5</v>
+        <v>12.7</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>58.34228266965062</v>
+        <v>60.62950880295568</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>18.34969203299106</v>
+        <v>17.93956228078887</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.7005021007546842</v>
+        <v>1.890413683160918</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.6250914991630516</v>
+        <v>0.0321734798898357</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1525</v>
+        <v>1410</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>602.0454597104983</v>
+        <v>609.1476411682221</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>68</v>
+        <v>26.2</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>58.01891269696729</v>
+        <v>55.18966469322424</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>29.05678443250714</v>
+        <v>17.98372371074881</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4476497750131713</v>
+        <v>3.127986603271433</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1801784844656857</v>
+        <v>0.2687552630880511</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1402</v>
+        <v>1513</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>594.7031702720147</v>
+        <v>607.1997643304441</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>29.1</v>
+        <v>178.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>61.37708204216877</v>
+        <v>58.34228266965062</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>19.65665000056883</v>
+        <v>18.34969203299106</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4053912658711125</v>
+        <v>0.7005021007546842</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.0013735895298284</v>
+        <v>-0.6250914991630516</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1308</v>
+        <v>1525</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>592.139086596426</v>
+        <v>602.0454597104983</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>15.5</v>
+        <v>68</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>65.48326461882374</v>
+        <v>58.01891269696729</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>18.30788289799606</v>
+        <v>29.05678443250714</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>4.756139994784522</v>
+        <v>0.4476497750131713</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.2107303424912137</v>
+        <v>0.1801784844656857</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1301</v>
+        <v>1402</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>588.94495109128</v>
+        <v>594.7031702720147</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>60.4</v>
+        <v>29.1</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>64.97013875849642</v>
+        <v>61.37708204216877</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>29.47373516879886</v>
+        <v>19.65665000056883</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.194495109128006</v>
+        <v>0.4053912658711125</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1.10117292415374</v>
+        <v>-0.0013735895298284</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1514</v>
+        <v>1308</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>584.7903575014797</v>
+        <v>592.139086596426</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>126.5</v>
+        <v>15.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>54.24969119954937</v>
+        <v>65.48326461882374</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>17.63731107158865</v>
+        <v>18.30788289799606</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>2.347257504789003</v>
+        <v>4.756139994784522</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.0372037262770959</v>
+        <v>0.2107303424912137</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1342</v>
+        <v>1301</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>583.0389026063267</v>
+        <v>588.94495109128</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>116.5</v>
+        <v>60.4</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>62.9357688376254</v>
+        <v>64.97013875849642</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>36.70960457608293</v>
+        <v>29.47373516879886</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.4286905795103881</v>
+        <v>1.194495109128006</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.5843502427585436</v>
+        <v>1.10117292415374</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1232</v>
+        <v>1514</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>581.2553021990025</v>
+        <v>584.7903575014797</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>149</v>
+        <v>126.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>63.84333850746058</v>
+        <v>54.24969119954937</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>35.2629621662671</v>
+        <v>17.63731107158865</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>3.425530219900239</v>
+        <v>2.347257504789003</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.6203907593764169</v>
+        <v>-0.0372037262770959</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1256</v>
+        <v>1342</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>574.4247524804164</v>
+        <v>583.0389026063267</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>199</v>
+        <v>116.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>66.88988642366314</v>
+        <v>62.9357688376254</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>16.87728445977221</v>
+        <v>36.70960457608293</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.375487855392069</v>
+        <v>0.4286905795103881</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1.642129466896827</v>
+        <v>-0.5843502427585436</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1531</v>
+        <v>1232</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>569.3618016131026</v>
+        <v>581.2553021990025</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>13.15</v>
+        <v>149</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>64.40894838007696</v>
+        <v>63.84333850746058</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>15.71830446419012</v>
+        <v>35.2629621662671</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.393500370853825</v>
+        <v>3.425530219900239</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0178302454028689</v>
+        <v>0.6203907593764169</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1460</v>
+        <v>1256</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>568.9431615774199</v>
+        <v>574.4247524804164</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>8.08</v>
+        <v>199</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>66.02054967064242</v>
+        <v>66.88988642366314</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>23.77849153393554</v>
+        <v>16.87728445977221</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>3.494316157741983</v>
+        <v>1.375487855392069</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.1249979281731046</v>
+        <v>1.642129466896827</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1437</v>
+        <v>1531</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>558.5901037741953</v>
+        <v>569.3618016131026</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>31.55</v>
+        <v>13.15</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>82.70398035596125</v>
+        <v>64.40894838007696</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>29.68279233983984</v>
+        <v>15.71830446419012</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.302228043588133</v>
+        <v>1.393500370853825</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.1584905584176045</v>
+        <v>0.0178302454028689</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1477</v>
+        <v>1460</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>552.7756074723828</v>
+        <v>568.9431615774199</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>230</v>
+        <v>8.08</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>58.62765557081574</v>
+        <v>66.02054967064242</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>18.53274419272362</v>
+        <v>23.77849153393554</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.9832927351001736</v>
+        <v>3.494316157741983</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>1.230010437895946</v>
+        <v>0.1249979281731046</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1474</v>
+        <v>1437</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>540.8573450681871</v>
+        <v>558.5901037741953</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>10.8</v>
+        <v>31.55</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>62.02748088869743</v>
+        <v>82.70398035596125</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>29.24665790412587</v>
+        <v>29.68279233983984</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>5.660678975487441</v>
+        <v>1.302228043588133</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.081244207926497</v>
+        <v>0.1584905584176045</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1452</v>
+        <v>1477</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>538.6838749542555</v>
+        <v>552.7756074723828</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>11.95</v>
+        <v>230</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>74.77805023278958</v>
+        <v>58.62765557081574</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>18.94918082268475</v>
+        <v>18.53274419272362</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2.604450980433981</v>
+        <v>0.9832927351001736</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.1075527341068516</v>
+        <v>1.230010437895946</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1229</v>
+        <v>1474</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>537.2448156550794</v>
+        <v>540.8573450681871</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>43.7</v>
+        <v>10.8</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>63.03568828065989</v>
+        <v>62.02748088869743</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>24.85956062189958</v>
+        <v>29.24665790412587</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.455359799991769</v>
+        <v>5.660678975487441</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.1583200801256067</v>
+        <v>0.081244207926497</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1529</v>
+        <v>1452</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>537.1394390779978</v>
+        <v>538.6838749542555</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>23.2</v>
+        <v>11.95</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>55.77953730203988</v>
+        <v>74.77805023278958</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>13.67951993819798</v>
+        <v>18.94918082268475</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.162116769096181</v>
+        <v>2.604450980433981</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0285148017600882</v>
+        <v>0.1075527341068516</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1414</v>
+        <v>1229</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>533.0421675356022</v>
+        <v>537.2448156550794</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>19.55</v>
+        <v>43.7</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>78.68745916350149</v>
+        <v>63.03568828065989</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>28.35044500442775</v>
+        <v>24.85956062189958</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.7101257335483352</v>
+        <v>1.455359799991769</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.2142985774798455</v>
+        <v>0.1583200801256067</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1468</v>
+        <v>1529</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>529.2944058845306</v>
+        <v>537.1394390779978</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>12.3</v>
+        <v>23.2</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>62.84905255408786</v>
+        <v>55.77953730203988</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>15.06644114305865</v>
+        <v>13.67951993819798</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.7532129494062144</v>
+        <v>1.162116769096181</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0500827683211788</v>
+        <v>0.0285148017600882</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1539</v>
+        <v>1414</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>巨庭</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>524.1312696057735</v>
+        <v>533.0421675356022</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>16.1</v>
+        <v>19.55</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>57.23369043772532</v>
+        <v>78.68745916350149</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>14.3268530557815</v>
+        <v>28.35044500442775</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.711840506526658</v>
+        <v>0.7101257335483352</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0543283626258832</v>
+        <v>0.2142985774798455</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1455</v>
+        <v>1468</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>517.5295260853906</v>
+        <v>529.2944058845306</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>10.9</v>
+        <v>12.3</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>70.45645034908966</v>
+        <v>62.84905255408786</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>42.76390378033046</v>
+        <v>15.06644114305865</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>4.480743713111029</v>
+        <v>0.7532129494062144</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.07760517361197659</v>
+        <v>0.0500827683211788</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1108</v>
+        <v>1539</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>巨庭</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>517.0394799436706</v>
+        <v>524.1312696057735</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>14.1</v>
+        <v>16.1</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>60.11684261260021</v>
+        <v>57.23369043772532</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>22.94208692168431</v>
+        <v>14.3268530557815</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.276495839348945</v>
+        <v>1.711840506526658</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0370903145634846</v>
+        <v>0.0543283626258832</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1446</v>
+        <v>1455</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>515.6288893023218</v>
+        <v>517.5295260853906</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>17.4</v>
+        <v>10.9</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>64.25355392424009</v>
+        <v>70.45645034908966</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>28.43127021494406</v>
+        <v>42.76390378033046</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2.239137521471571</v>
+        <v>4.480743713111029</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0772037082102876</v>
+        <v>0.07760517361197659</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1338</v>
+        <v>1108</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>500.4577056091499</v>
+        <v>517.0394799436706</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>17.65</v>
+        <v>14.1</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>65.40645045778291</v>
+        <v>60.11684261260021</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>18.431749285363</v>
+        <v>22.94208692168431</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5772395149516446</v>
+        <v>1.276495839348945</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0421853406054094</v>
+        <v>0.0370903145634846</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1307</v>
+        <v>1446</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>498.2362269171293</v>
+        <v>515.6288893023218</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>33.15</v>
+        <v>17.4</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>42.4021693697895</v>
+        <v>64.25355392424009</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>19.84044104724043</v>
+        <v>28.43127021494406</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.680576362954454</v>
+        <v>2.239137521471571</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.3062826050264701</v>
+        <v>0.0772037082102876</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1231</v>
+        <v>1338</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>487.9842370547829</v>
+        <v>500.4577056091499</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>89.09999999999999</v>
+        <v>17.65</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>58.20976120285775</v>
+        <v>65.40645045778291</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>16.33954216645438</v>
+        <v>18.431749285363</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.228212650225434</v>
+        <v>0.5772395149516446</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.1311561094549347</v>
+        <v>0.0421853406054094</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1504</v>
+        <v>1307</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>485.8539493386789</v>
+        <v>498.2362269171293</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>73.09999999999999</v>
+        <v>33.15</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>54.14444958583309</v>
+        <v>42.4021693697895</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>13.32713553238816</v>
+        <v>19.84044104724043</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.648334003191685</v>
+        <v>1.680576362954454</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.0487142314128991</v>
+        <v>-0.3062826050264701</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1506</v>
+        <v>1231</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>483.9626801449247</v>
+        <v>487.9842370547829</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>10.55</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>58.68427920064006</v>
+        <v>58.20976120285775</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>28.9520872000628</v>
+        <v>16.33954216645438</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.7880613650682413</v>
+        <v>1.228212650225434</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0544705560857495</v>
+        <v>0.1311561094549347</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1305</v>
+        <v>1504</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>481.8076725821583</v>
+        <v>485.8539493386789</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>14.1</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>58.32387605607314</v>
+        <v>54.14444958583309</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>13.32313899432388</v>
+        <v>13.32713553238816</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.981550625472354</v>
+        <v>1.648334003191685</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.1791304652544085</v>
+        <v>-0.0487142314128991</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1315</v>
+        <v>1506</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>478.9034618799057</v>
+        <v>483.9626801449247</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>64.3</v>
+        <v>10.55</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>72.68476776333019</v>
+        <v>58.68427920064006</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>15.21150898709279</v>
+        <v>28.9520872000628</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5389984949676681</v>
+        <v>0.7880613650682413</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.2425969839432445</v>
+        <v>0.0544705560857495</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1423</v>
+        <v>1305</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>474.0991119233322</v>
+        <v>481.8076725821583</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>36.65</v>
+        <v>14.1</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>28.04401884382116</v>
+        <v>58.32387605607314</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>36.25740329495934</v>
+        <v>13.32313899432388</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.0449965643255472</v>
+        <v>1.981550625472354</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.428027004135179</v>
+        <v>0.1791304652544085</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1463</v>
+        <v>1315</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>463.8807908533943</v>
+        <v>478.9034618799057</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>17.75</v>
+        <v>64.3</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>53.76555035324828</v>
+        <v>72.68476776333019</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>23.47986511479347</v>
+        <v>15.21150898709279</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.749086013927681</v>
+        <v>0.5389984949676681</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0477637636311126</v>
+        <v>0.2425969839432445</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1459</v>
+        <v>1423</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>460.5417032336314</v>
+        <v>474.0991119233322</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>12.15</v>
+        <v>36.65</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>64.80498076332708</v>
+        <v>28.04401884382116</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>17.98958359408161</v>
+        <v>36.25740329495934</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.462382537732357</v>
+        <v>0.0449965643255472</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0396051118737557</v>
+        <v>-0.428027004135179</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1532</v>
+        <v>1463</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>459.9151911950629</v>
+        <v>463.8807908533943</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>23.6</v>
+        <v>17.75</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>63.76836358762343</v>
+        <v>53.76555035324828</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>30.52180854413053</v>
+        <v>23.47986511479347</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.5978762755942464</v>
+        <v>1.749086013927681</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0476072438537716</v>
+        <v>0.0477637636311126</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1304</v>
+        <v>1459</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>459.8202638130767</v>
+        <v>460.5417032336314</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>14.7</v>
+        <v>12.15</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>60.77319839075883</v>
+        <v>64.80498076332708</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>17.46612985507807</v>
+        <v>17.98958359408161</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>3.96617710696232</v>
+        <v>1.462382537732357</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.209726155538681</v>
+        <v>0.0396051118737557</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1466</v>
+        <v>1532</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>458.4112858955917</v>
+        <v>459.9151911950629</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>18.3</v>
+        <v>23.6</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>77.54217921556952</v>
+        <v>63.76836358762343</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>24.1165781004356</v>
+        <v>30.52180854413053</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>4.941128589559171</v>
+        <v>0.5978762755942464</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.5137187088971811</v>
+        <v>-0.0476072438537716</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1475</v>
+        <v>1304</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>456.9998254201149</v>
+        <v>459.8202638130767</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>27.95</v>
+        <v>14.7</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>63.62824532030996</v>
+        <v>60.77319839075883</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>17.13591551979998</v>
+        <v>17.46612985507807</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3657627017512456</v>
+        <v>3.96617710696232</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0745001192156768</v>
+        <v>0.209726155538681</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1568</v>
+        <v>1466</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>454.1718242809979</v>
+        <v>458.4112858955917</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>37.5</v>
+        <v>18.3</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>46.68481509488645</v>
+        <v>77.54217921556952</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>30.57177435858648</v>
+        <v>24.1165781004356</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.8934338906824456</v>
+        <v>4.941128589559171</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.88083388109584</v>
+        <v>0.5137187088971811</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1442</v>
+        <v>1475</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>449.1071908124849</v>
+        <v>456.9998254201149</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>28.7</v>
+        <v>27.95</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>62.97775616077564</v>
+        <v>63.62824532030996</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>19.26867134471202</v>
+        <v>17.13591551979998</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.037967617234107</v>
+        <v>0.3657627017512456</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.1130781418736672</v>
+        <v>0.0745001192156768</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1417</v>
+        <v>1568</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>445.8380245984797</v>
+        <v>454.1718242809979</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>9.1</v>
+        <v>37.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>69.28386991946795</v>
+        <v>46.68481509488645</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>20.47497041524246</v>
+        <v>30.57177435858648</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.650515367745646</v>
+        <v>0.8934338906824456</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.08458695238099</v>
+        <v>-0.88083388109584</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1540</v>
+        <v>1442</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>444.244121003711</v>
+        <v>449.1071908124849</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>22.8</v>
+        <v>28.7</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>62.24729128364352</v>
+        <v>62.97775616077564</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>17.48298763595066</v>
+        <v>19.26867134471202</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.427411604578928</v>
+        <v>1.037967617234107</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.09612306157205699</v>
+        <v>0.1130781418736672</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1512</v>
+        <v>1417</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>411.9444060156366</v>
+        <v>445.8380245984797</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>7.21</v>
+        <v>9.1</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>58.81763532379334</v>
+        <v>69.28386991946795</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>11.25780772143152</v>
+        <v>20.47497041524246</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.950830092601672</v>
+        <v>1.650515367745646</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0380332945742706</v>
+        <v>0.08458695238099</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1236</v>
+        <v>1540</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>409.2703340357604</v>
+        <v>444.244121003711</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>25.55</v>
+        <v>22.8</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.39739446159163</v>
+        <v>62.24729128364352</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>10.4707568564754</v>
+        <v>17.48298763595066</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.561365113957897</v>
+        <v>1.427411604578928</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.0390344226874577</v>
+        <v>0.09612306157205699</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1445</v>
+        <v>1435</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>404.5648497225424</v>
+        <v>425.3029272126688</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>12.05</v>
+        <v>26.8</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>57.02054013772187</v>
+        <v>58.57804766425631</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>29.32545868392685</v>
+        <v>15.73193030129978</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.25648497225424</v>
+        <v>0.6925142646265648</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.1968014574895449</v>
+        <v>1.705152689149426</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1110</v>
+        <v>1512</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>401.5575245922186</v>
+        <v>411.9444060156366</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>15.9</v>
+        <v>7.21</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>60.08861080441242</v>
+        <v>58.81763532379334</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>32.23772726288504</v>
+        <v>11.25780772143152</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.58984773069894</v>
+        <v>1.950830092601672</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0267962159236586</v>
+        <v>0.0380332945742706</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1454</v>
+        <v>1236</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>401.204267202547</v>
+        <v>409.2703340357604</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>13.1</v>
+        <v>25.55</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>55.48492405245126</v>
+        <v>51.39739446159163</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>15.21019986411618</v>
+        <v>10.4707568564754</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.200831980036955</v>
+        <v>1.561365113957897</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0358663384382527</v>
+        <v>-0.0390344226874577</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1526</v>
+        <v>1445</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>399.9703129656635</v>
+        <v>404.5648497225424</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>15</v>
+        <v>12.05</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>57.72580858864955</v>
+        <v>57.02054013772187</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>21.90852646865573</v>
+        <v>29.32545868392685</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.49871073567628</v>
+        <v>1.25648497225424</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.1023360884138103</v>
+        <v>0.1968014574895449</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>393.1689064746751</v>
+        <v>401.5575245922186</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>13.75</v>
+        <v>15.9</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>59.56569991758965</v>
+        <v>60.08861080441242</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>12.75101760064126</v>
+        <v>32.23772726288504</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.00835316112343</v>
+        <v>1.58984773069894</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0016083574606444</v>
+        <v>0.0267962159236586</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1324</v>
+        <v>1454</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>380.3914613301212</v>
+        <v>401.204267202547</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>10.6</v>
+        <v>13.1</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>53.969710810656</v>
+        <v>55.48492405245126</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>21.65994625709132</v>
+        <v>15.21019986411618</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.511571218543716</v>
+        <v>1.200831980036955</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0337381154494081</v>
+        <v>0.0358663384382527</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1220</v>
+        <v>1526</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>368.8489534599981</v>
+        <v>399.9703129656635</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>11.85</v>
+        <v>15</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>56.1858357723542</v>
+        <v>57.72580858864955</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>25.4050996484556</v>
+        <v>21.90852646865573</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.5954712127729346</v>
+        <v>1.49871073567628</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0450490754380553</v>
+        <v>0.1023360884138103</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1472</v>
+        <v>1103</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>366.7231977506919</v>
+        <v>393.1689064746751</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>87.90000000000001</v>
+        <v>13.75</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>48.42552641021284</v>
+        <v>59.56569991758965</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>10.63451386204436</v>
+        <v>12.75101760064126</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.1324206185449447</v>
+        <v>1.00835316112343</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.320438660632204</v>
+        <v>-0.0016083574606444</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1309</v>
+        <v>1324</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>364.1668982466248</v>
+        <v>380.3914613301212</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>15.6</v>
+        <v>10.6</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>51.23499756513546</v>
+        <v>53.969710810656</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>13.83530742631722</v>
+        <v>21.65994625709132</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>3.256828474778622</v>
+        <v>1.511571218543716</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.235427844550545</v>
+        <v>0.0337381154494081</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1109</v>
+        <v>1220</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>360.6383288299671</v>
+        <v>368.8489534599981</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>14.8</v>
+        <v>11.85</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>57.2937910778541</v>
+        <v>56.1858357723542</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>17.73117394304494</v>
+        <v>25.4050996484556</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4798556763436186</v>
+        <v>0.5954712127729346</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0351564859971434</v>
+        <v>0.0450490754380553</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1521</v>
+        <v>1472</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>354.7785597521495</v>
+        <v>366.7231977506919</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>26.25</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>52.14611251229494</v>
+        <v>48.42552641021284</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>13.91927205899827</v>
+        <v>10.63451386204436</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.3932728109284227</v>
+        <v>0.1324206185449447</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0734547063822782</v>
+        <v>-0.320438660632204</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1451</v>
+        <v>1309</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>352.2075528552498</v>
+        <v>364.1668982466248</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>17.45</v>
+        <v>15.6</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>66.38098476005788</v>
+        <v>51.23499756513546</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>18.91217272610001</v>
+        <v>13.83530742631722</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.249288605076645</v>
+        <v>3.256828474778622</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0690306697476577</v>
+        <v>0.235427844550545</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1470</v>
+        <v>1109</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>344.8712564737881</v>
+        <v>360.6383288299671</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>21.7</v>
+        <v>14.8</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>51.97994071237811</v>
+        <v>57.2937910778541</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>8.577466152956596</v>
+        <v>17.73117394304494</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.1018044844875416</v>
+        <v>0.4798556763436186</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.8076320169279612</v>
+        <v>0.0351564859971434</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1467</v>
+        <v>1521</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>337.2422456047213</v>
+        <v>354.7785597521495</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>9.31</v>
+        <v>26.25</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>75.04541955045852</v>
+        <v>52.14611251229494</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>27.88292683668265</v>
+        <v>13.91927205899827</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>8.028116113628412</v>
+        <v>0.3932728109284227</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.2451877580226323</v>
+        <v>-0.0734547063822782</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1528</v>
+        <v>1451</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>330.1847409344728</v>
+        <v>352.2075528552498</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>24.05</v>
+        <v>17.45</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>43.5209649713189</v>
+        <v>66.38098476005788</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>9.017108973648517</v>
+        <v>18.91217272610001</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.504165641757793</v>
+        <v>1.249288605076645</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0483049650536764</v>
+        <v>0.0690306697476577</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1438</v>
+        <v>1470</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>327.2559136482554</v>
+        <v>344.8712564737881</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>22.2</v>
+        <v>21.7</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>49.34698688180348</v>
+        <v>51.97994071237811</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>20.41506815855505</v>
+        <v>8.577466152956596</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.181675652237863</v>
+        <v>0.1018044844875416</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.019561915795697</v>
+        <v>0.8076320169279612</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1533</v>
+        <v>1467</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>319.5050448833283</v>
+        <v>337.2422456047213</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>37.5</v>
+        <v>9.31</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>53.71058107965632</v>
+        <v>75.04541955045852</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>29.30938171586915</v>
+        <v>27.88292683668265</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5731903486448814</v>
+        <v>8.028116113628412</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.1401677601136799</v>
+        <v>0.2451877580226323</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1436</v>
+        <v>1528</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>316.7792885558387</v>
+        <v>330.1847409344728</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>45.6</v>
+        <v>24.05</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>48.08498416883077</v>
+        <v>43.5209649713189</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>17.25624071179359</v>
+        <v>9.017108973648517</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.5486567911394349</v>
+        <v>0.504165641757793</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.1008471063345201</v>
+        <v>-0.0483049650536764</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1538</v>
+        <v>1438</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>312.809628993225</v>
+        <v>327.2559136482554</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>10.7</v>
+        <v>22.2</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>52.3242932046189</v>
+        <v>49.34698688180348</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>7.655454082774533</v>
+        <v>20.41506815855505</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>2.593941489879068</v>
+        <v>0.181675652237863</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.4461969217493453</v>
+        <v>0.019561915795697</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1457</v>
+        <v>1533</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>312.284019508376</v>
+        <v>319.5050448833283</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>14.7</v>
+        <v>37.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>58.18227860117003</v>
+        <v>53.71058107965632</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>15.25476806125357</v>
+        <v>29.30938171586915</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5942390752378827</v>
+        <v>0.5731903486448814</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0441547293094937</v>
+        <v>-0.1401677601136799</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1203</v>
+        <v>1436</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>311.2060265285266</v>
+        <v>316.7792885558387</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>42.9</v>
+        <v>45.6</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>48.94599606431932</v>
+        <v>48.08498416883077</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>11.86059296156935</v>
+        <v>17.25624071179359</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.127256093703619</v>
+        <v>0.5486567911394349</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0118006438924295</v>
+        <v>0.1008471063345201</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1516</v>
+        <v>1538</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>309.8980791381792</v>
+        <v>312.809628993225</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>18.65</v>
+        <v>10.7</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>33.37697280246392</v>
+        <v>52.3242932046189</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>33.49212065932637</v>
+        <v>7.655454082774533</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.628488214648494</v>
+        <v>2.593941489879068</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.1663314722233214</v>
+        <v>-0.4461969217493453</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1527</v>
+        <v>1457</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>307.2859036011808</v>
+        <v>312.284019508376</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>33.9</v>
+        <v>14.7</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>59.88419011333112</v>
+        <v>58.18227860117003</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>17.47532586663867</v>
+        <v>15.25476806125357</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.31075700628297</v>
+        <v>0.5942390752378827</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0494350188100222</v>
+        <v>0.0441547293094937</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1582</v>
+        <v>1203</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>297.8945995683836</v>
+        <v>311.2060265285266</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>82.09999999999999</v>
+        <v>42.9</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>35.16999232357269</v>
+        <v>48.94599606431932</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>21.64626773910089</v>
+        <v>11.86059296156935</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.3241476406348588</v>
+        <v>1.127256093703619</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.6356148703525104</v>
+        <v>-0.0118006438924295</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1416</v>
+        <v>1516</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>296.1874672095886</v>
+        <v>309.8980791381792</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>11.2</v>
+        <v>18.65</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>54.50609389726327</v>
+        <v>33.37697280246392</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>21.97610018762328</v>
+        <v>33.49212065932637</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.7546763828682821</v>
+        <v>1.628488214648494</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0361317960316942</v>
+        <v>-0.1663314722233214</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1219</v>
+        <v>1527</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>295.8826328745265</v>
+        <v>307.2859036011808</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>12.35</v>
+        <v>33.9</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>38.52319162493159</v>
+        <v>59.88419011333112</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>29.2614906433455</v>
+        <v>17.47532586663867</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>3.005727583482033</v>
+        <v>1.31075700628297</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0102688215223259</v>
+        <v>0.0494350188100222</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1215</v>
+        <v>1582</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>293.1226652233144</v>
+        <v>297.8945995683836</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>113</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>36.73029753003603</v>
+        <v>35.16999232357269</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>46.7280416490655</v>
+        <v>21.64626773910089</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.946763259044494</v>
+        <v>0.3241476406348588</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.5191222871728236</v>
+        <v>-0.6356148703525104</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1471</v>
+        <v>1416</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>290.6347561097967</v>
+        <v>296.1874672095886</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>49.0485910636845</v>
+        <v>54.50609389726327</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>11.17707806729806</v>
+        <v>21.97610018762328</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.8422161350746231</v>
+        <v>0.7546763828682821</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0072077576313594</v>
+        <v>0.0361317960316942</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1439</v>
+        <v>1219</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>288.0560231777735</v>
+        <v>295.8826328745265</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>24.2</v>
+        <v>12.35</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>45.61274004744695</v>
+        <v>38.52319162493159</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>11.74853082569297</v>
+        <v>29.2614906433455</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.2837796205896645</v>
+        <v>3.005727583482033</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0323662404378021</v>
+        <v>0.0102688215223259</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1441</v>
+        <v>1215</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>282.6263752260123</v>
+        <v>293.1226652233144</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>9.550000000000001</v>
+        <v>113</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>57.58674374635356</v>
+        <v>36.73029753003603</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>24.4319279370956</v>
+        <v>46.7280416490655</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.401324711944824</v>
+        <v>0.946763259044494</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.08182038157205</v>
+        <v>0.5191222871728236</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, bb_squeeze_breakout</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1413</v>
+        <v>1471</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>278.3024609493913</v>
+        <v>290.6347561097967</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>9.5</v>
+        <v>10.9</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>52.85531038612211</v>
+        <v>49.0485910636845</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>18.60965903393511</v>
+        <v>11.17707806729806</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>2.032405044145728</v>
+        <v>0.8422161350746231</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.008449201147486299</v>
+        <v>0.0072077576313594</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1319</v>
+        <v>1439</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>262.616701340958</v>
+        <v>288.0560231777735</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>78</v>
+        <v>24.2</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>39.92356313575866</v>
+        <v>45.61274004744695</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>30.85268271226188</v>
+        <v>11.74853082569297</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.4293525339299824</v>
+        <v>0.2837796205896645</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-1.785129187186168</v>
+        <v>-0.0323662404378021</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1340</v>
+        <v>1441</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>257.194740772151</v>
+        <v>282.6263752260123</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>5.83</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>60.2377261834054</v>
+        <v>57.58674374635356</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>17.92255468831176</v>
+        <v>24.4319279370956</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>4.153486900035173</v>
+        <v>1.401324711944824</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0324263687426837</v>
+        <v>0.08182038157205</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, bb_squeeze_breakout</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1473</v>
+        <v>1413</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>248.2488270350324</v>
+        <v>278.3024609493913</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>20.8</v>
+        <v>9.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>56.68795809129538</v>
+        <v>52.85531038612211</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>19.895166924936</v>
+        <v>18.60965903393511</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.321987350885257</v>
+        <v>2.032405044145728</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.1218583478007775</v>
+        <v>0.008449201147486299</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, cci_momentum, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1432</v>
+        <v>1319</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>244.3774798330726</v>
+        <v>262.616701340958</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>15.3</v>
+        <v>78</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>32.45783018143342</v>
+        <v>39.92356313575866</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>32.3579982795905</v>
+        <v>30.85268271226188</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5469874816857635</v>
+        <v>0.4293525339299824</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.1527482259214987</v>
+        <v>-1.785129187186168</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1213</v>
+        <v>1340</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>237.449383535912</v>
+        <v>257.194740772151</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>7.58</v>
+        <v>5.83</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>49.06174251569068</v>
+        <v>60.2377261834054</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>6.745728782843905</v>
+        <v>17.92255468831176</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>3.360656042684447</v>
+        <v>4.153486900035173</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0539487142087341</v>
+        <v>0.0324263687426837</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>volume_break, rsi_strong, market_above_ma60, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1443</v>
+        <v>1473</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>233.6904555557232</v>
+        <v>248.2488270350324</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>26.4</v>
+        <v>20.8</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>50.33423709138921</v>
+        <v>56.68795809129538</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>16.48085220594125</v>
+        <v>19.895166924936</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.4421765738081311</v>
+        <v>1.321987350885257</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.158900645543037</v>
+        <v>0.1218583478007775</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1522</v>
+        <v>1432</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>228.2077715995217</v>
+        <v>244.3774798330726</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>30.55</v>
+        <v>15.3</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>47.56406204103516</v>
+        <v>32.45783018143342</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>13.23145500932187</v>
+        <v>32.3579982795905</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.7919466372114227</v>
+        <v>0.5469874816857635</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0240362953165776</v>
+        <v>-0.1527482259214987</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1519</v>
+        <v>1213</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>228.1787359690753</v>
+        <v>237.449383535912</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>773</v>
+        <v>7.58</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>42.06910306995715</v>
+        <v>49.06174251569068</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>13.00281593977322</v>
+        <v>6.745728782843905</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.070470742562604</v>
+        <v>3.360656042684447</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-2.069747202852554</v>
+        <v>0.0539487142087341</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1316</v>
+        <v>1443</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>219.9959052947559</v>
+        <v>233.6904555557232</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>10.75</v>
+        <v>26.4</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>52.04158158003855</v>
+        <v>50.33423709138921</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>14.57692920798484</v>
+        <v>16.48085220594125</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.7454447000348784</v>
+        <v>0.4421765738081311</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0450738696739593</v>
+        <v>-0.158900645543037</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1537</v>
+        <v>1522</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>215.7512427411039</v>
+        <v>228.2077715995217</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>126.5</v>
+        <v>30.55</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>52.94851897204804</v>
+        <v>47.56406204103516</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>18.86521798733728</v>
+        <v>13.23145500932187</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.7779072833395255</v>
+        <v>0.7919466372114227</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.08149285253031049</v>
+        <v>-0.0240362953165776</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1218</v>
+        <v>1519</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>214.6554803730019</v>
+        <v>228.1787359690753</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>17.3</v>
+        <v>773</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>27.91036547064596</v>
+        <v>42.06910306995715</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>37.32765261946101</v>
+        <v>13.00281593977322</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.7544302567102599</v>
+        <v>1.070470742562604</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0653972914900655</v>
+        <v>-2.069747202852554</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1456</v>
+        <v>1316</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>205.2192882783966</v>
+        <v>219.9959052947559</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>14.3</v>
+        <v>10.75</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>51.58411433118467</v>
+        <v>52.04158158003855</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>18.46284510537393</v>
+        <v>14.57692920798484</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.7448325123885772</v>
+        <v>0.7454447000348784</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.100476232531332</v>
+        <v>0.0450738696739593</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1541</v>
+        <v>1537</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>204.9656311782554</v>
+        <v>215.7512427411039</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>21.6</v>
+        <v>126.5</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>49.08451149854976</v>
+        <v>52.94851897204804</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>11.200000282623</v>
+        <v>18.86521798733728</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.687566560381674</v>
+        <v>0.7779072833395255</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0329901332825332</v>
+        <v>-0.08149285253031049</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1341</v>
+        <v>1218</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>186.931469999487</v>
+        <v>214.6554803730019</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>57.7</v>
+        <v>17.3</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>50.60781639128381</v>
+        <v>27.91036547064596</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>22.18748037271629</v>
+        <v>37.32765261946101</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.6527908812599881</v>
+        <v>0.7544302567102599</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-1.23486255281605</v>
+        <v>-0.0653972914900655</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6781,21 +6781,21 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1453</v>
+        <v>1456</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>186.606087613474</v>
+        <v>205.2192882783966</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>11.55</v>
+        <v>14.3</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>52.66447759886199</v>
+        <v>51.58411433118467</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>22.95983833876884</v>
+        <v>18.46284510537393</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.5916336038890745</v>
+        <v>0.7448325123885772</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.0018928266286597</v>
+        <v>-0.100476232531332</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1104</v>
+        <v>1541</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>184.911872752365</v>
+        <v>204.9656311782554</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>27.55</v>
+        <v>21.6</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>45.34035139907147</v>
+        <v>49.08451149854976</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>29.04119738149799</v>
+        <v>11.200000282623</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.6157835619217911</v>
+        <v>1.687566560381674</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.09660188540410659</v>
+        <v>0.0329901332825332</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1535</v>
+        <v>1341</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>176.1207469765989</v>
+        <v>186.931469999487</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>50.3</v>
+        <v>57.7</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>52.57254242587953</v>
+        <v>50.60781639128381</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>28.70905048718156</v>
+        <v>22.18748037271629</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.2732347748496646</v>
+        <v>0.6527908812599881</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0393139696989147</v>
+        <v>-1.23486255281605</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1476</v>
+        <v>1453</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>167.169020471303</v>
+        <v>186.606087613474</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>323</v>
+        <v>11.55</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>46.34370815826784</v>
+        <v>52.66447759886199</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>17.55556840499089</v>
+        <v>22.95983833876884</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.4962144805563739</v>
+        <v>0.5916336038890745</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.186767955505962</v>
+        <v>-0.0018928266286597</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1524</v>
+        <v>1104</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>165.1492372432638</v>
+        <v>184.911872752365</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>29.5</v>
+        <v>27.55</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>48.69517044468084</v>
+        <v>45.34035139907147</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>13.79894908824459</v>
+        <v>29.04119738149799</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.057442696553354</v>
+        <v>0.6157835619217911</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.0160122747993045</v>
+        <v>-0.09660188540410659</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1225</v>
+        <v>1535</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>161.5779843361732</v>
+        <v>176.1207469765989</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>28.05</v>
+        <v>50.3</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>36.12433721336844</v>
+        <v>52.57254242587953</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>17.85365308241942</v>
+        <v>28.70905048718156</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.006916230331985</v>
+        <v>0.2732347748496646</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.2469524370028759</v>
+        <v>0.0393139696989147</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1569</v>
+        <v>1476</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>153.7939224877231</v>
+        <v>167.169020471303</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>49.5</v>
+        <v>323</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>52.58398354461587</v>
+        <v>46.34370815826784</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>16.95326303808414</v>
+        <v>17.55556840499089</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1.177553620903615</v>
+        <v>0.4962144805563739</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.3588128229662886</v>
+        <v>-0.186767955505962</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1101</v>
+        <v>1524</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>151.0561357101973</v>
+        <v>165.1492372432638</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>23.7</v>
+        <v>29.5</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>44.44217161520643</v>
+        <v>48.69517044468084</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>12.91957837944014</v>
+        <v>13.79894908824459</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.4794163716042133</v>
+        <v>1.057442696553354</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0884297763588672</v>
+        <v>-0.0160122747993045</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1233</v>
+        <v>1225</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>140.6016674261847</v>
+        <v>161.5779843361732</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>28.15</v>
+        <v>28.05</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>49.63732976511387</v>
+        <v>36.12433721336844</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>10.51344424071976</v>
+        <v>17.85365308241942</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>1.402772234672889</v>
+        <v>1.006916230331985</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.0561883767326426</v>
+        <v>-0.2469524370028759</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7258,21 +7258,21 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1530</v>
+        <v>1569</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>79.30306589208364</v>
+        <v>153.7939224877231</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>29.75</v>
+        <v>49.5</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>50.34193056026423</v>
+        <v>52.58398354461587</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>18.29844904718384</v>
+        <v>16.95326303808414</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.5509759665504377</v>
+        <v>1.177553620903615</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L129" s="2" t="n">
         <v>0</v>
@@ -7301,62 +7301,221 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.1063404388342648</v>
+        <v>0.3588128229662886</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60</t>
+          <t>market_above_ma60, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>151.0561357101973</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>44.44217161520643</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>12.91957837944014</v>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>0.4794163716042133</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N130" s="2" t="n">
+        <v>-0.0884297763588672</v>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>1233</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>天仁</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>140.6016674261847</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>49.63732976511387</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>10.51344424071976</v>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>1.402772234672889</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N131" s="2" t="n">
+        <v>0.0561883767326426</v>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>1530</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>亞崴</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>79.30306589208364</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>50.34193056026423</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>18.29844904718384</v>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>0.5509759665504377</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N132" s="2" t="n">
+        <v>-0.1063404388342648</v>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
         <v>1325</v>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>恆大</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D130" s="2" t="n">
+      <c r="C133" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D133" s="2" t="n">
         <v>74.2146663224642</v>
       </c>
-      <c r="E130" s="2" t="n">
+      <c r="E133" s="2" t="n">
         <v>25.35</v>
       </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H130" s="2" t="n">
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H133" s="2" t="n">
         <v>46.79799026381954</v>
       </c>
-      <c r="I130" s="2" t="n">
+      <c r="I133" s="2" t="n">
         <v>22.2829968963118</v>
       </c>
-      <c r="J130" s="2" t="n">
+      <c r="J133" s="2" t="n">
         <v>0.4123141067914605</v>
       </c>
-      <c r="K130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N130" s="2" t="n">
+      <c r="K133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N133" s="2" t="n">
         <v>-0.0045813486394379</v>
       </c>
-      <c r="O130" s="2" t="inlineStr">
+      <c r="O133" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, adx_trending</t>
         </is>
